--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -1,37 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_F3222DCEA08A4C9A6976DB97F14DE766E6606446" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{009BD7B4-C43D-4DD9-AC85-F5B72744DDEF}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="3570" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2055" yWindow="3570" windowWidth="21600" windowHeight="11295" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
-    <sheet name="static_regulatory_values" sheetId="2" r:id="rId2"/>
-    <sheet name="calculated_regulatory_values" sheetId="4" r:id="rId3"/>
-    <sheet name="diss_metals_hard_parameters" sheetId="9" r:id="rId4"/>
-    <sheet name="pick_list" sheetId="3" r:id="rId5"/>
-    <sheet name="questions" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId7"/>
+    <sheet name="ReadMe" sheetId="8" state="visible" r:id="rId1"/>
+    <sheet name="static_regulatory_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="calculated_regulatory_values" sheetId="4" state="visible" r:id="rId3"/>
+    <sheet name="diss_metals_hard_parameters" sheetId="9" state="visible" r:id="rId4"/>
+    <sheet name="pick_list" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="questions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+    <comment ref="I16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -41,7 +34,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Author:</t>
+          <t xml:space="preserve">Author:</t>
         </r>
         <r>
           <rPr>
@@ -60,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -623,6 +616,30 @@
   </si>
   <si>
     <t>Nitrate + Nitrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_metals_aquatic_life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEC;USEPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquatic_life_chronic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEC 2008; USEPA 1976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value in mg/L (not ug/L) — iron analysis data is reported in mg/L</t>
   </si>
 </sst>
 </file>
@@ -632,67 +649,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color indexed="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -704,17 +664,71 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
-      <u/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b/>
     </font>
   </fonts>
   <fills count="7">
@@ -726,13 +740,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="42"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="22"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -745,12 +765,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="41"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,99 +790,94 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1150,1334 +1159,1364 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>142</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P62"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="15"/>
-    <col min="3" max="3" width="26.140625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="38.42578125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="15" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="15"/>
-    <col min="9" max="10" width="26.5703125" style="15" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="15" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="1" width="18.85546875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="26.5703125" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="26.5703125" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="B2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="B3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="4" t="n">
         <v>4300</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="B8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="15" t="s">
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="13" t="s">
+      <c r="B12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K12" s="15" t="s">
+      <c r="K12" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="P12" s="15" t="s">
+      <c r="P12" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="15" t="s">
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="13" t="s">
+      <c r="B14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K14" s="15" t="s">
+      <c r="K14" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" s="15" t="s">
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="30" t="s">
+      <c r="B15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="15" t="s">
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="15" t="s">
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="15" t="s">
+      <c r="K17" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="15" t="s">
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="15" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="15" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="13" t="s">
+      <c r="B20" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K20" s="15" t="s">
+      <c r="K20" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A21" s="15" t="s">
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="15" t="s">
+      <c r="B21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K21" s="15" t="s">
+      <c r="K21" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="15" t="s">
+      <c r="B22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="H22" s="15" t="s">
+      <c r="H22" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K22" s="15" t="s">
+      <c r="K22" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="K23" s="15" t="s">
+      <c r="K23" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="16" t="s">
+      <c r="B24" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="K24" s="15" t="s">
+      <c r="K24" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="16" t="s">
+      <c r="B25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="H25" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="K25" s="15" t="s">
+      <c r="K25" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A26" s="15" t="s">
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="15" t="s">
+      <c r="B26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K26" s="15" t="s">
+      <c r="K26" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="15" t="s">
+      <c r="B27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="4" t="n">
         <v>5000</v>
       </c>
-      <c r="H27" s="15" t="s">
+      <c r="H27" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K27" s="15" t="s">
+      <c r="K27" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B28" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="15" t="s">
+      <c r="B28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K28" s="15" t="s">
+      <c r="K28" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="15" t="s">
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H29" s="15" t="s">
+      <c r="H29" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="I29" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A30" s="15" t="s">
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="15" t="s">
+      <c r="B30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="H30" s="15" t="s">
+      <c r="H30" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K30" s="15" t="s">
+      <c r="K30" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A31" s="15" t="s">
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="15" t="s">
+      <c r="B31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="K31" s="15" t="s">
+      <c r="K31" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="B32" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K32" s="15" t="s">
+      <c r="K32" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="15" t="s">
+      <c r="B33" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="K33" s="15" t="s">
+      <c r="K33" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A34" s="15" t="s">
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="13" t="s">
+      <c r="B34" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="K34" s="15" t="s">
+      <c r="K34" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A35" s="15" t="s">
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="15" t="s">
+      <c r="B35" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="H35" s="15" t="s">
+      <c r="H35" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K35" s="15" t="s">
+      <c r="K35" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A36" s="15" t="s">
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H36" s="15" t="s">
+      <c r="H36" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K36" s="15" t="s">
+      <c r="K36" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A37" s="15" t="s">
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="H37" s="15" t="s">
+      <c r="H37" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="I37" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K37" s="15" t="s">
+      <c r="K37" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A38" s="15" t="s">
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="K38" s="15" t="s">
+      <c r="K38" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A39" s="15" t="s">
+    <row r="39" ht="63.75" customHeight="1">
+      <c r="A39" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="16" t="s">
+      <c r="B39" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="J39" s="31" t="s">
+      <c r="J39" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="K39" s="15" t="s">
+      <c r="K39" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A40" s="15" t="s">
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K40" s="15" t="s">
+      <c r="K40" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="15" t="s">
+      <c r="B41" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="15" t="s">
+      <c r="H41" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="I41" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K41" s="15" t="s">
+      <c r="K41" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A42" s="15" t="s">
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="K42" s="15" t="s">
+      <c r="K42" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A43" s="15" t="s">
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K43" s="15" t="s">
+      <c r="K43" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J44" s="15" t="s">
+      <c r="J44" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="K44" s="15" t="s">
+      <c r="K44" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" s="15" t="s">
+      <c r="B45" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H45" s="15" t="s">
+      <c r="H45" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="I45" s="32" t="s">
+      <c r="I45" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="K45" s="15" t="s">
+      <c r="K45" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="K46" s="15" t="s">
+      <c r="K46" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="K47" s="15" t="s">
+      <c r="K47" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A48" s="15" t="s">
+    <row r="48" ht="14.25" customHeight="1">
+      <c r="A48" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B48" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="15" t="s">
+      <c r="B48" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H48" s="15" t="s">
+      <c r="H48" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I48" s="15" t="s">
+      <c r="I48" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K48" s="15" t="s">
+      <c r="K48" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="15" t="s">
+    <row r="49" ht="14.25" customHeight="1">
+      <c r="A49" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="K49" s="15" t="s">
+      <c r="K49" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A50" s="15" t="s">
+    <row r="50" ht="14.25" customHeight="1">
+      <c r="A50" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B50" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C50" s="15" t="s">
+      <c r="B50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="H50" s="15" t="s">
+      <c r="H50" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I50" s="15" t="s">
+      <c r="I50" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K50" s="15" t="s">
+      <c r="K50" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="15" t="s">
+    <row r="51">
+      <c r="A51" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B51" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" s="15" t="s">
+      <c r="B51" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="H51" s="15" t="s">
+      <c r="H51" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="I51" s="15" t="s">
+      <c r="I51" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="15" t="s">
+    <row r="52">
+      <c r="A52" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B52" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C52" s="15" t="s">
+      <c r="B52" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D52" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="4" t="n">
         <v>8.5</v>
       </c>
-      <c r="H52" s="15" t="s">
+      <c r="H52" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="I52" s="15" t="s">
+      <c r="I52" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I62" s="15" t="s">
+    <row r="53">
+      <c r="A53" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" t="s">
+        <v>190</v>
+      </c>
+      <c r="E53" t="s">
+        <v>191</v>
+      </c>
+      <c r="F53"/>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>192</v>
+      </c>
+      <c r="I53" t="s">
+        <v>193</v>
+      </c>
+      <c r="J53" t="s">
+        <v>194</v>
+      </c>
+      <c r="K53"/>
+    </row>
+    <row r="62">
+      <c r="I62" s="4" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I45" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="I45" r:id="rId1h"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -2485,339 +2524,338 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="15"/>
-    <col min="2" max="2" width="26.140625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="18" style="24" customWidth="1"/>
-    <col min="6" max="6" width="31.28515625" customWidth="1"/>
-    <col min="7" max="7" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="31.28515625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="33.7109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1">
+      <c r="A1" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="19" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+    <row r="2" ht="31.5" customHeight="1">
+      <c r="A2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="10" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="15" t="s">
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="15" t="s">
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="12" t="s">
         <v>138</v>
       </c>
       <c r="G4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="15" t="s">
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="15" t="s">
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="12" t="s">
         <v>51</v>
       </c>
       <c r="G6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="13" t="s">
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="13" t="s">
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F8" t="s">
         <v>37</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>0.316</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="13" t="s">
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="13" t="s">
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F10" t="s">
         <v>53</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>0.86</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="15" t="s">
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="15" t="s">
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F12" t="s">
         <v>38</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>0.96</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="15" t="s">
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="15" t="s">
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>0.96</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="15" t="s">
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="15" t="s">
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F16" t="s">
@@ -2827,40 +2865,40 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="15" t="s">
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="15" t="s">
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F18" t="s">
@@ -2870,383 +2908,385 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="15" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="15" t="s">
+      <c r="C19" s="5"/>
+      <c r="D19" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="15" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="15" t="s">
+      <c r="C20" s="5"/>
+      <c r="D20" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F20" t="s">
         <v>41</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>0.998</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="15" t="s">
+    <row r="21">
+      <c r="A21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="15" t="s">
+      <c r="C21" s="5"/>
+      <c r="D21" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="15" t="s">
+    <row r="22">
+      <c r="A22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="15" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F22" t="s">
         <v>58</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>0.997</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="15" t="s">
+    <row r="23">
+      <c r="A23" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="15" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F23" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="15" t="s">
+    <row r="24">
+      <c r="A24" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="15" t="s">
+      <c r="C24" s="5"/>
+      <c r="D24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F24" t="s">
         <v>42</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>0.92200000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="15" t="s">
+    <row r="25">
+      <c r="A25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="15" t="s">
+      <c r="C25" s="5"/>
+      <c r="D25" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="15" t="s">
+    <row r="26">
+      <c r="A26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="15" t="s">
+      <c r="C26" s="5"/>
+      <c r="D26" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>5</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>0.92200000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="15" t="s">
+    <row r="27">
+      <c r="A27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="15" t="s">
+      <c r="C27" s="5"/>
+      <c r="D27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F27" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="15" t="s">
+    <row r="28">
+      <c r="A28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="15" t="s">
+      <c r="C28" s="5"/>
+      <c r="D28" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F28" t="s">
         <v>43</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="15" t="s">
+    <row r="29">
+      <c r="A29" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F29" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="15" t="s">
+    <row r="30">
+      <c r="A30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F30" t="s">
         <v>44</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>0.97799999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="15" t="s">
+    <row r="31">
+      <c r="A31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="9" t="s">
         <v>134</v>
       </c>
       <c r="F31" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="15" t="s">
+    <row r="32">
+      <c r="A32" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F32" t="s">
         <v>44</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>0.98599999999999999</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="16"/>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="16"/>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="16"/>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C36" s="16"/>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="16"/>
+    <row r="33">
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="5"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="13" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="12" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+    <row r="2" ht="47.25" customHeight="1">
+      <c r="A2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="10" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
       <c r="B3" t="s">
         <v>82</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" t="s">
         <v>86</v>
       </c>
       <c r="B4" t="s">
         <v>86</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>1.0165999999999999</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>-3.9239999999999999</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0.7409</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>-4.7190000000000003</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="14" t="s">
         <v>153</v>
       </c>
       <c r="H4" t="s">
@@ -3256,86 +3296,86 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>141</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>0.81899999999999995</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>3.7256</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0.81899999999999995</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>0.68479999999999996</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>0.316</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>0.86</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>149</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>0.98199999999999998</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>88</v>
       </c>
       <c r="B7" t="s">
         <v>88</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>0.94220000000000004</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>0.85450000000000004</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>-1.702</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>0.96</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>0.96</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>91</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>1.2729999999999999</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>-1.46</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>1.2729999999999999</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>-4.7050000000000001</v>
       </c>
       <c r="G8" t="s">
@@ -3345,7 +3385,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -3356,1010 +3396,1013 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>93</v>
       </c>
       <c r="B10" t="s">
         <v>93</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>0.84599999999999997</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>2.2549999999999999</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>0.84599999999999997</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>5.8400000000000001E-2</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>0.998</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>0.997</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>100</v>
       </c>
       <c r="B11" t="s">
         <v>100</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>1.72</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>-6.59</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>0.85</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>110</v>
       </c>
       <c r="B12" t="s">
         <v>110</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>0.84730000000000005</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>0.88400000000000001</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>0.84730000000000005</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>0.88400000000000001</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>0.97799999999999998</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>0.98599999999999999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1">
+      <c r="A1" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>156</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A6:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="G6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>132</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="31.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="50" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="31.5703125" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="19" customFormat="1" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="76.5" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="29"/>
+      <c r="I1" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="29" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="1"/>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="1"/>
-      <c r="C3" s="6"/>
-    </row>
-    <row r="4" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="16.5" customHeight="1">
+      <c r="B2" s="15"/>
+      <c r="C2" s="27"/>
+    </row>
+    <row r="3" ht="16.5" customHeight="1">
+      <c r="B3" s="15"/>
+      <c r="C3" s="27"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1">
       <c r="A4" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="4" t="s">
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
       <c r="A5" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="5">
+      <c r="C5" s="20"/>
+      <c r="D5" s="26" t="n">
         <v>750</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="9" t="s">
+      <c r="E5" s="25"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="25"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1">
       <c r="A6" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1">
       <c r="A7" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="25" t="n">
         <v>340</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" ht="16.5" customHeight="1">
       <c r="A8" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="26" t="n">
         <v>2000</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1">
       <c r="A9" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1">
       <c r="A10" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1">
       <c r="A11" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4" t="s">
+      <c r="H11" s="25"/>
+      <c r="I11" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" ht="16.5" customHeight="1">
       <c r="A12" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="5">
+      <c r="C12" s="20"/>
+      <c r="D12" s="26" t="n">
         <v>860000</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="5">
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="26" t="n">
         <v>230000</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1">
       <c r="A13" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="4">
+      <c r="C13" s="20"/>
+      <c r="D13" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="4">
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+    </row>
+    <row r="14" ht="16.5" customHeight="1">
       <c r="A14" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+    </row>
+    <row r="15" ht="16.5" customHeight="1">
       <c r="A15" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="4" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="25" t="n">
         <v>0.316</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4" t="s">
+      <c r="H15" s="25"/>
+      <c r="I15" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="16" t="n">
         <v>0.86</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" ht="16.5" customHeight="1">
       <c r="A16" t="s">
         <v>128</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="4">
+      <c r="C16" s="20"/>
+      <c r="D16" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="4">
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1">
       <c r="A17" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12" s="23" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1">
       <c r="A18" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21" t="s">
+      <c r="C18" s="22"/>
+      <c r="D18" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="23" t="n">
         <v>0.96</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21" t="s">
+      <c r="H18" s="22"/>
+      <c r="I18" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="J18" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="22">
+      <c r="K18" s="23" t="n">
         <v>0.96</v>
       </c>
-      <c r="L18" s="21" t="s">
+      <c r="L18" s="22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" ht="16.5" customHeight="1">
       <c r="A19" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="4" t="s">
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" ht="16.5" customHeight="1">
       <c r="A20" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="26" t="n">
         <v>4000</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1">
       <c r="A21" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="5">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1">
       <c r="A22" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="4" t="s">
+      <c r="C22" s="20"/>
+      <c r="D22" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4" t="s">
+      <c r="H22" s="25"/>
+      <c r="I22" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" ht="16.5" customHeight="1">
       <c r="A23" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1">
       <c r="A24" t="s">
         <v>128</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1">
       <c r="A25" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="25" t="n">
         <v>1.4</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="4">
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="25" t="n">
         <v>0.77</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1">
       <c r="A26" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1">
       <c r="A27" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="16" t="n">
         <v>0.998</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4" t="s">
+      <c r="H27" s="25"/>
+      <c r="I27" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="16" t="n">
         <v>0.997</v>
       </c>
-      <c r="L27" s="4" t="s">
+      <c r="L27" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" ht="16.5" customHeight="1">
       <c r="A28" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1">
       <c r="A29" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1">
       <c r="A30" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+    </row>
+    <row r="31" ht="31.5" customHeight="1">
       <c r="A31" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="16" t="n">
         <v>0.92200000000000004</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4">
+      <c r="H31" s="25"/>
+      <c r="I31" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="16" t="n">
         <v>0.92200000000000004</v>
       </c>
-      <c r="L31" s="4" t="s">
+      <c r="L31" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" ht="16.5" customHeight="1">
       <c r="A32" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="4" t="s">
+      <c r="C32" s="20"/>
+      <c r="D32" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="16" t="n">
         <v>0.85</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="25"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="20"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1">
       <c r="A33" t="s">
         <v>128</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1">
       <c r="A34" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1">
       <c r="A35" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="4" t="s">
+      <c r="C35" s="20"/>
+      <c r="D35" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="16" t="n">
         <v>0.97799999999999998</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4" t="s">
+      <c r="H35" s="25"/>
+      <c r="I35" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="J35" s="4" t="s">
+      <c r="J35" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="16" t="n">
         <v>0.98599999999999999</v>
       </c>
-      <c r="L35" s="4" t="s">
+      <c r="L35" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -3,22 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="3570" windowWidth="21600" windowHeight="11295" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="2055" yWindow="3570" windowWidth="21600" windowHeight="11295" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" state="visible" r:id="rId1"/>
-    <sheet name="static_regulatory_values" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="calculated_regulatory_values" sheetId="4" state="visible" r:id="rId3"/>
-    <sheet name="diss_metals_hard_parameters" sheetId="9" state="visible" r:id="rId4"/>
-    <sheet name="pick_list" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="questions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId7"/>
+    <sheet name="static_regulatory_values" sheetId="11" state="visible" r:id="rId8"/>
+    <sheet name="calculated_regulatory_values" sheetId="4" state="visible" r:id="rId2"/>
+    <sheet name="diss_metals_hard_parameters" sheetId="9" state="visible" r:id="rId3"/>
+    <sheet name="pick_list" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="questions" sheetId="6" state="visible" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId6"/>
+    <sheet name="standard_types" sheetId="10" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="340">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -640,6 +641,443 @@
   </si>
   <si>
     <t xml:space="preserve">Value in mg/L (not ug/L) — iron analysis data is reported in mg/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">display_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulatory_authority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquaculture_maximum_water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquaculture (maximum pH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquaculture_minimum_water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquaculture (minimum pH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquaculture_water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquaculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquatic life – chronic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEC, USEPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drinking_water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drinking water (MCL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USEPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drinking_water_single_sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drinking water (single-sample limit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fw_acute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquatic life – acute (freshwater)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fw_chronic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquatic life – chronic (freshwater)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">harvest_aquatic_life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvest for human consumption (aquatic life)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">irrigation_water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irrigation water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noncarc_aquatic_org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-carcinogenic risk (aquatic organisms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noncarc_water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-carcinogenic risk (water ingestion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recreation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recreation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recreation_single_sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recreation (single-sample limit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secondary_water_recreation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary contact recreation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stock_water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temp_all_freshwaters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All freshwaters (maximum)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temp_egg_fry_spawning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egg and fry incubation and spawning areas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temp_rearing_migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rearing areas and migration routes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wildlife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wildlife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">static_category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parameter_agency_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parameter_baseline_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parameter_form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reg_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reg_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">special_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data_entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">static_metals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aluminum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aluminum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ug/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010 toxicsbook.xls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BM 20230220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where the pH is &gt;= 7.0 and the hardness &gt; 50 ppm measured as CaCO3, the chronic aluminum standard will be equal to the acute, 750 μg/l as total recoverable aluminum. Otherwise the chronic standard is 87 μg/l .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">antimony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antimony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arsenic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arsenic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BM 20230227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydocarbons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benzene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beryllium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beryllium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydrocarbons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benzene, toluene, ethyl benzene, xylenes mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benzene, toluene, ethyl benzene, xylenes mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 AAC 70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.epa.gov/system/files/documents/2023-05/akwqs-chapter70-2023.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BM 20231129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cadmium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadmium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chromium (total)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chromium (total), as distinct from other chemical forms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cobalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethylbenzene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bacteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecal Coliform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cfu/100ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://dec.alaska.gov/water/water-quality/standards/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BM 20250115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecal Coliform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molybdenum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molybdenum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nickel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nickel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o-xylene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o-Xylene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P &amp; M -Xylene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nutrients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphorus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phosphorus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">potassium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potassium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selenium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selenium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No general standard, but see 18 AAC 70.236(b)
+WATERSHED, Anchorage WWTP, 1.9 μg/l (acute)
+measured as dissolved metal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thallium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thallium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titanium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">part of BTEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Nitrate and Nitrite (as nitrogen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nitrate + Nitrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 AAC 70 Water Quality Standards April 26, 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Phosphorus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total suspended solids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vanadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xylenes (total)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zinc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zinc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://dec.alaska.gov/media/eovgrgs5/18-aac-70.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field_bio_standards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature, water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deg_c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEC 18 AAC 70.020</t>
   </si>
 </sst>
 </file>
@@ -649,7 +1087,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -661,61 +1099,37 @@
       <sz val="14"/>
       <color indexed="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <b/>
     </font>
     <font>
@@ -727,7 +1141,6 @@
       <sz val="14"/>
       <color indexed="12"/>
       <name val="Arial"/>
-      <family val="2"/>
       <b/>
     </font>
   </fonts>
@@ -795,85 +1208,79 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1184,1350 +1591,6 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="38.42578125" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="26.5703125" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>4300</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" ht="63.75" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>187</v>
-      </c>
-      <c r="B53" t="s">
-        <v>188</v>
-      </c>
-      <c r="C53" t="s">
-        <v>189</v>
-      </c>
-      <c r="D53" t="s">
-        <v>190</v>
-      </c>
-      <c r="E53" t="s">
-        <v>191</v>
-      </c>
-      <c r="F53"/>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="s">
-        <v>192</v>
-      </c>
-      <c r="I53" t="s">
-        <v>193</v>
-      </c>
-      <c r="J53" t="s">
-        <v>194</v>
-      </c>
-      <c r="K53"/>
-    </row>
-    <row r="62">
-      <c r="I62" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I45" r:id="rId1h"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
     <col min="2" max="2" width="26.140625" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="26.42578125" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" hidden="0" customWidth="1"/>
@@ -2537,70 +1600,70 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="2" ht="31.5" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="3" t="s">
         <v>138</v>
       </c>
       <c r="G4" t="s">
@@ -2608,42 +1671,42 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="3" t="s">
         <v>51</v>
       </c>
       <c r="G6" t="s">
@@ -2651,19 +1714,19 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F7" t="s">
@@ -2671,19 +1734,19 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F8" t="s">
@@ -2694,19 +1757,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F9" t="s">
@@ -2714,19 +1777,19 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F10" t="s">
@@ -2737,19 +1800,19 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F11" t="s">
@@ -2757,19 +1820,19 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F12" t="s">
@@ -2780,19 +1843,19 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F13" t="s">
@@ -2800,19 +1863,19 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F14" t="s">
@@ -2823,39 +1886,39 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F16" t="s">
@@ -2866,19 +1929,19 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F17" t="s">
@@ -2886,19 +1949,19 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F18" t="s">
@@ -2909,17 +1972,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="4" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F19" t="s">
@@ -2927,17 +1990,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="4" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F20" t="s">
@@ -2948,17 +2011,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="4" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F21" t="s">
@@ -2966,17 +2029,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="4" t="s">
+      <c r="C22" s="7"/>
+      <c r="D22" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F22" t="s">
@@ -2987,17 +2050,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="4" t="s">
+      <c r="C23" s="7"/>
+      <c r="D23" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F23" t="s">
@@ -3005,17 +2068,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="4" t="s">
+      <c r="C24" s="7"/>
+      <c r="D24" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F24" t="s">
@@ -3026,17 +2089,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="4" t="s">
+      <c r="C25" s="7"/>
+      <c r="D25" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F25" t="n">
@@ -3044,17 +2107,17 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="4" t="s">
+      <c r="C26" s="7"/>
+      <c r="D26" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F26" t="n">
@@ -3065,17 +2128,17 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="4" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F27" t="s">
@@ -3083,17 +2146,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="4" t="s">
+      <c r="C28" s="7"/>
+      <c r="D28" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F28" t="s">
@@ -3104,19 +2167,19 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F29" t="s">
@@ -3124,19 +2187,19 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F30" t="s">
@@ -3147,19 +2210,19 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F31" t="s">
@@ -3167,19 +2230,19 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F32" t="s">
@@ -3190,19 +2253,19 @@
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="5"/>
+      <c r="C33" s="7"/>
     </row>
     <row r="34">
-      <c r="C34" s="5"/>
+      <c r="C34" s="7"/>
     </row>
     <row r="35">
-      <c r="C35" s="5"/>
+      <c r="C35" s="7"/>
     </row>
     <row r="36">
-      <c r="C36" s="5"/>
+      <c r="C36" s="7"/>
     </row>
     <row r="37">
-      <c r="C37" s="5"/>
+      <c r="C37" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3210,7 +2273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -3223,33 +2286,33 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="9" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="2" ht="47.25" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="8" t="s">
         <v>148</v>
       </c>
     </row>
@@ -3286,7 +2349,7 @@
       <c r="F4" t="n">
         <v>-4.7190000000000003</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="10" t="s">
         <v>153</v>
       </c>
       <c r="H4" t="s">
@@ -3468,6 +2531,67 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3476,54 +2600,14 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>114</v>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>113</v>
+      <c r="G6" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -3533,27 +2617,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="6">
-      <c r="G6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -3570,144 +2633,144 @@
   </cols>
   <sheetData>
     <row r="1" ht="76.5" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29" t="s">
+      <c r="H1" s="25"/>
+      <c r="I1" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="L1" s="25" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1">
-      <c r="B2" s="15"/>
-      <c r="C2" s="27"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" ht="16.5" customHeight="1">
-      <c r="B3" s="15"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="23"/>
     </row>
     <row r="4" ht="16.5" customHeight="1">
       <c r="A4" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="25" t="s">
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="26" t="n">
+      <c r="C5" s="16"/>
+      <c r="D5" s="22" t="n">
         <v>750</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="30" t="s">
+      <c r="E5" s="21"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="25"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="21" t="n">
         <v>340</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25" t="n">
+      <c r="H7" s="21"/>
+      <c r="I7" s="21" t="n">
         <v>150</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="25" t="n">
+      <c r="K7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3715,95 +2778,95 @@
       <c r="A8" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="22" t="n">
         <v>2000</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25" t="s">
+      <c r="H11" s="21"/>
+      <c r="I11" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K11" s="25" t="s">
+      <c r="K11" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="L11" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3811,103 +2874,103 @@
       <c r="A12" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="26" t="n">
+      <c r="C12" s="16"/>
+      <c r="D12" s="22" t="n">
         <v>860000</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="26" t="n">
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="22" t="n">
         <v>230000</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="25" t="n">
+      <c r="C13" s="16"/>
+      <c r="D13" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="25" t="n">
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="25" t="s">
+      <c r="C15" s="16"/>
+      <c r="D15" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="F15" s="21" t="n">
         <v>0.316</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25" t="s">
+      <c r="H15" s="21"/>
+      <c r="I15" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="16" t="n">
+      <c r="K15" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="L15" s="25" t="s">
+      <c r="L15" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3915,77 +2978,77 @@
       <c r="A16" t="s">
         <v>128</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="25" t="n">
+      <c r="C16" s="16"/>
+      <c r="D16" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="25" t="n">
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
     </row>
     <row r="17" ht="16.5" customHeight="1">
       <c r="A17" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
     </row>
     <row r="18" ht="16.5" customHeight="1">
       <c r="A18" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22" t="s">
+      <c r="C18" s="18"/>
+      <c r="D18" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="19" t="n">
         <v>0.96</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22" t="s">
+      <c r="H18" s="18"/>
+      <c r="I18" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="J18" s="22" t="s">
+      <c r="J18" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="23" t="n">
+      <c r="K18" s="19" t="n">
         <v>0.96</v>
       </c>
-      <c r="L18" s="22" t="s">
+      <c r="L18" s="18" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3993,97 +3056,97 @@
       <c r="A19" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="25" t="s">
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
     </row>
     <row r="20" ht="16.5" customHeight="1">
       <c r="A20" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="22" t="n">
         <v>4000</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
     </row>
     <row r="21" ht="16.5" customHeight="1">
       <c r="A21" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="26" t="n">
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="22" t="n">
         <v>1000</v>
       </c>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
     </row>
     <row r="22" ht="16.5" customHeight="1">
       <c r="A22" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="25" t="s">
+      <c r="C22" s="16"/>
+      <c r="D22" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25" t="s">
+      <c r="H22" s="21"/>
+      <c r="I22" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="25" t="s">
+      <c r="K22" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="L22" s="25" t="s">
+      <c r="L22" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4091,117 +3154,117 @@
       <c r="A23" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
     </row>
     <row r="24" ht="16.5" customHeight="1">
       <c r="A24" t="s">
         <v>128</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
     </row>
     <row r="25" ht="16.5" customHeight="1">
       <c r="A25" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="25" t="n">
+      <c r="D25" s="21" t="n">
         <v>1.4</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="25" t="n">
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="21" t="n">
         <v>0.77</v>
       </c>
-      <c r="J25" s="25" t="s">
+      <c r="J25" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
     </row>
     <row r="26" ht="16.5" customHeight="1">
       <c r="A26" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
     </row>
     <row r="27" ht="16.5" customHeight="1">
       <c r="A27" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="E27" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="12" t="n">
         <v>0.998</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25" t="s">
+      <c r="H27" s="21"/>
+      <c r="I27" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J27" s="25" t="s">
+      <c r="J27" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K27" s="16" t="n">
+      <c r="K27" s="12" t="n">
         <v>0.997</v>
       </c>
-      <c r="L27" s="25" t="s">
+      <c r="L27" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4209,95 +3272,95 @@
       <c r="A28" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
     </row>
     <row r="29" ht="16.5" customHeight="1">
       <c r="A29" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
     </row>
     <row r="30" ht="16.5" customHeight="1">
       <c r="A30" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="22" t="n">
         <v>1000</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
     </row>
     <row r="31" ht="31.5" customHeight="1">
       <c r="A31" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="E31" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="12" t="n">
         <v>0.92200000000000004</v>
       </c>
-      <c r="G31" s="25" t="s">
+      <c r="G31" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25" t="n">
+      <c r="H31" s="21"/>
+      <c r="I31" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="J31" s="25" t="s">
+      <c r="J31" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K31" s="16" t="n">
+      <c r="K31" s="12" t="n">
         <v>0.92200000000000004</v>
       </c>
-      <c r="L31" s="25" t="s">
+      <c r="L31" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4305,97 +3368,97 @@
       <c r="A32" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="25" t="s">
+      <c r="C32" s="16"/>
+      <c r="D32" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="25" t="s">
+      <c r="E32" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="12" t="n">
         <v>0.85</v>
       </c>
-      <c r="G32" s="25" t="s">
+      <c r="G32" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H32" s="25"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="20"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="16"/>
     </row>
     <row r="33" ht="16.5" customHeight="1">
       <c r="A33" t="s">
         <v>128</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="25" t="n">
+      <c r="C33" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
     </row>
     <row r="34" ht="16.5" customHeight="1">
       <c r="A34" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
     </row>
     <row r="35" ht="16.5" customHeight="1">
       <c r="A35" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="25" t="s">
+      <c r="C35" s="16"/>
+      <c r="D35" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="E35" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="12" t="n">
         <v>0.97799999999999998</v>
       </c>
-      <c r="G35" s="25" t="s">
+      <c r="G35" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25" t="s">
+      <c r="H35" s="21"/>
+      <c r="I35" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J35" s="25" t="s">
+      <c r="J35" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K35" s="16" t="n">
+      <c r="K35" s="12" t="n">
         <v>0.98599999999999999</v>
       </c>
-      <c r="L35" s="25" t="s">
+      <c r="L35" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4405,4 +3468,2024 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <legacyDrawing r:id="rIdvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B13" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" t="s">
+        <v>232</v>
+      </c>
+      <c r="C16" t="s">
+        <v>201</v>
+      </c>
+      <c r="D16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B17" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B19" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>239</v>
+      </c>
+      <c r="B20" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D21" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J1" t="s">
+        <v>251</v>
+      </c>
+      <c r="K1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2"/>
+      <c r="G2" t="n">
+        <v>750</v>
+      </c>
+      <c r="H2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J2"/>
+      <c r="K2" t="s">
+        <v>259</v>
+      </c>
+      <c r="L2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F3"/>
+      <c r="G3" t="n">
+        <v>87</v>
+      </c>
+      <c r="H3" t="s">
+        <v>257</v>
+      </c>
+      <c r="I3" t="s">
+        <v>258</v>
+      </c>
+      <c r="J3" t="s">
+        <v>260</v>
+      </c>
+      <c r="K3" t="s">
+        <v>259</v>
+      </c>
+      <c r="L3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4"/>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>257</v>
+      </c>
+      <c r="I4" t="s">
+        <v>258</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4" t="s">
+        <v>259</v>
+      </c>
+      <c r="L4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5"/>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>257</v>
+      </c>
+      <c r="I5" t="s">
+        <v>258</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5" t="s">
+        <v>259</v>
+      </c>
+      <c r="L5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6" t="n">
+        <v>4300</v>
+      </c>
+      <c r="H6" t="s">
+        <v>257</v>
+      </c>
+      <c r="I6" t="s">
+        <v>258</v>
+      </c>
+      <c r="J6"/>
+      <c r="K6" t="s">
+        <v>259</v>
+      </c>
+      <c r="L6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7"/>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I7" t="s">
+        <v>258</v>
+      </c>
+      <c r="J7"/>
+      <c r="K7" t="s">
+        <v>265</v>
+      </c>
+      <c r="L7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E8" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
+        <v>257</v>
+      </c>
+      <c r="I8" t="s">
+        <v>258</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8" t="s">
+        <v>265</v>
+      </c>
+      <c r="L8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" t="s">
+        <v>264</v>
+      </c>
+      <c r="E9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="s">
+        <v>257</v>
+      </c>
+      <c r="I9" t="s">
+        <v>258</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9" t="s">
+        <v>265</v>
+      </c>
+      <c r="L9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" t="s">
+        <v>267</v>
+      </c>
+      <c r="E10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10"/>
+      <c r="G10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H10" t="s">
+        <v>257</v>
+      </c>
+      <c r="I10" t="s">
+        <v>258</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10" t="s">
+        <v>265</v>
+      </c>
+      <c r="L10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11" t="s">
+        <v>269</v>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11" t="s">
+        <v>265</v>
+      </c>
+      <c r="L11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E12" t="s">
+        <v>209</v>
+      </c>
+      <c r="F12"/>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="s">
+        <v>257</v>
+      </c>
+      <c r="I12" t="s">
+        <v>258</v>
+      </c>
+      <c r="J12"/>
+      <c r="K12" t="s">
+        <v>265</v>
+      </c>
+      <c r="L12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" t="s">
+        <v>271</v>
+      </c>
+      <c r="E13" t="s">
+        <v>221</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" t="s">
+        <v>257</v>
+      </c>
+      <c r="I13" t="s">
+        <v>258</v>
+      </c>
+      <c r="J13"/>
+      <c r="K13" t="s">
+        <v>265</v>
+      </c>
+      <c r="L13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" t="s">
+        <v>272</v>
+      </c>
+      <c r="D14" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" t="s">
+        <v>221</v>
+      </c>
+      <c r="F14"/>
+      <c r="G14" t="n">
+        <v>750</v>
+      </c>
+      <c r="H14" t="s">
+        <v>257</v>
+      </c>
+      <c r="I14" t="s">
+        <v>258</v>
+      </c>
+      <c r="J14"/>
+      <c r="K14" t="s">
+        <v>265</v>
+      </c>
+      <c r="L14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" t="s">
+        <v>275</v>
+      </c>
+      <c r="D15" t="s">
+        <v>276</v>
+      </c>
+      <c r="E15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>257</v>
+      </c>
+      <c r="I15" t="s">
+        <v>277</v>
+      </c>
+      <c r="J15" t="s">
+        <v>278</v>
+      </c>
+      <c r="K15" t="s">
+        <v>279</v>
+      </c>
+      <c r="L15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>254</v>
+      </c>
+      <c r="B16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" t="s">
+        <v>280</v>
+      </c>
+      <c r="D16" t="s">
+        <v>281</v>
+      </c>
+      <c r="E16" t="s">
+        <v>209</v>
+      </c>
+      <c r="F16"/>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>257</v>
+      </c>
+      <c r="I16" t="s">
+        <v>258</v>
+      </c>
+      <c r="J16"/>
+      <c r="K16" t="s">
+        <v>265</v>
+      </c>
+      <c r="L16"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" t="s">
+        <v>201</v>
+      </c>
+      <c r="C17" t="s">
+        <v>280</v>
+      </c>
+      <c r="D17" t="s">
+        <v>281</v>
+      </c>
+      <c r="E17" t="s">
+        <v>233</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s">
+        <v>257</v>
+      </c>
+      <c r="I17" t="s">
+        <v>258</v>
+      </c>
+      <c r="J17"/>
+      <c r="K17" t="s">
+        <v>265</v>
+      </c>
+      <c r="L17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18" t="s">
+        <v>280</v>
+      </c>
+      <c r="D18" t="s">
+        <v>281</v>
+      </c>
+      <c r="E18" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s">
+        <v>257</v>
+      </c>
+      <c r="I18" t="s">
+        <v>258</v>
+      </c>
+      <c r="J18"/>
+      <c r="K18" t="s">
+        <v>265</v>
+      </c>
+      <c r="L18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>254</v>
+      </c>
+      <c r="B19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" t="s">
+        <v>282</v>
+      </c>
+      <c r="D19" t="s">
+        <v>283</v>
+      </c>
+      <c r="E19" t="s">
+        <v>209</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I19" t="s">
+        <v>258</v>
+      </c>
+      <c r="J19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K19" t="s">
+        <v>265</v>
+      </c>
+      <c r="L19"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>254</v>
+      </c>
+      <c r="B20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" t="s">
+        <v>283</v>
+      </c>
+      <c r="E20" t="s">
+        <v>221</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" t="s">
+        <v>257</v>
+      </c>
+      <c r="I20" t="s">
+        <v>258</v>
+      </c>
+      <c r="J20"/>
+      <c r="K20" t="s">
+        <v>265</v>
+      </c>
+      <c r="L20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C21" t="s">
+        <v>285</v>
+      </c>
+      <c r="D21" t="s">
+        <v>286</v>
+      </c>
+      <c r="E21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" t="s">
+        <v>257</v>
+      </c>
+      <c r="I21" t="s">
+        <v>258</v>
+      </c>
+      <c r="J21"/>
+      <c r="K21" t="s">
+        <v>265</v>
+      </c>
+      <c r="L21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>254</v>
+      </c>
+      <c r="B22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" t="s">
+        <v>287</v>
+      </c>
+      <c r="D22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E22" t="s">
+        <v>221</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22" t="n">
+        <v>200</v>
+      </c>
+      <c r="H22" t="s">
+        <v>257</v>
+      </c>
+      <c r="I22" t="s">
+        <v>258</v>
+      </c>
+      <c r="J22"/>
+      <c r="K22" t="s">
+        <v>265</v>
+      </c>
+      <c r="L22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>274</v>
+      </c>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23" t="s">
+        <v>289</v>
+      </c>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23" t="s">
+        <v>265</v>
+      </c>
+      <c r="L23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>290</v>
+      </c>
+      <c r="B24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24"/>
+      <c r="D24" t="s">
+        <v>291</v>
+      </c>
+      <c r="E24" t="s">
+        <v>231</v>
+      </c>
+      <c r="F24"/>
+      <c r="G24" t="n">
+        <v>400</v>
+      </c>
+      <c r="H24" t="s">
+        <v>292</v>
+      </c>
+      <c r="I24" t="s">
+        <v>293</v>
+      </c>
+      <c r="J24"/>
+      <c r="K24" t="s">
+        <v>294</v>
+      </c>
+      <c r="L24"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>290</v>
+      </c>
+      <c r="B25" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25"/>
+      <c r="D25" t="s">
+        <v>295</v>
+      </c>
+      <c r="E25" t="s">
+        <v>219</v>
+      </c>
+      <c r="F25"/>
+      <c r="G25" t="n">
+        <v>31</v>
+      </c>
+      <c r="H25" t="s">
+        <v>292</v>
+      </c>
+      <c r="I25" t="s">
+        <v>293</v>
+      </c>
+      <c r="J25"/>
+      <c r="K25" t="s">
+        <v>294</v>
+      </c>
+      <c r="L25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" t="s">
+        <v>296</v>
+      </c>
+      <c r="D26" t="s">
+        <v>297</v>
+      </c>
+      <c r="E26" t="s">
+        <v>233</v>
+      </c>
+      <c r="F26"/>
+      <c r="G26" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" t="s">
+        <v>257</v>
+      </c>
+      <c r="I26" t="s">
+        <v>258</v>
+      </c>
+      <c r="J26"/>
+      <c r="K26" t="s">
+        <v>265</v>
+      </c>
+      <c r="L26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" t="s">
+        <v>296</v>
+      </c>
+      <c r="D27" t="s">
+        <v>297</v>
+      </c>
+      <c r="E27" t="s">
+        <v>221</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H27" t="s">
+        <v>257</v>
+      </c>
+      <c r="I27" t="s">
+        <v>258</v>
+      </c>
+      <c r="J27"/>
+      <c r="K27" t="s">
+        <v>265</v>
+      </c>
+      <c r="L27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>254</v>
+      </c>
+      <c r="B28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28" t="s">
+        <v>298</v>
+      </c>
+      <c r="D28" t="s">
+        <v>299</v>
+      </c>
+      <c r="E28" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28"/>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="s">
+        <v>257</v>
+      </c>
+      <c r="I28" t="s">
+        <v>258</v>
+      </c>
+      <c r="J28"/>
+      <c r="K28" t="s">
+        <v>265</v>
+      </c>
+      <c r="L28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>254</v>
+      </c>
+      <c r="B29" t="s">
+        <v>201</v>
+      </c>
+      <c r="C29" t="s">
+        <v>300</v>
+      </c>
+      <c r="D29" t="s">
+        <v>301</v>
+      </c>
+      <c r="E29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F29"/>
+      <c r="G29" t="n">
+        <v>100</v>
+      </c>
+      <c r="H29" t="s">
+        <v>257</v>
+      </c>
+      <c r="I29" t="s">
+        <v>258</v>
+      </c>
+      <c r="J29"/>
+      <c r="K29" t="s">
+        <v>265</v>
+      </c>
+      <c r="L29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C30" t="s">
+        <v>300</v>
+      </c>
+      <c r="D30" t="s">
+        <v>301</v>
+      </c>
+      <c r="E30" t="s">
+        <v>221</v>
+      </c>
+      <c r="F30"/>
+      <c r="G30" t="n">
+        <v>200</v>
+      </c>
+      <c r="H30" t="s">
+        <v>257</v>
+      </c>
+      <c r="I30" t="s">
+        <v>258</v>
+      </c>
+      <c r="J30"/>
+      <c r="K30" t="s">
+        <v>265</v>
+      </c>
+      <c r="L30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>274</v>
+      </c>
+      <c r="B31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" t="s">
+        <v>302</v>
+      </c>
+      <c r="D31" t="s">
+        <v>303</v>
+      </c>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31" t="s">
+        <v>265</v>
+      </c>
+      <c r="L31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>274</v>
+      </c>
+      <c r="B32" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" t="s">
+        <v>304</v>
+      </c>
+      <c r="D32" t="s">
+        <v>304</v>
+      </c>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32" t="s">
+        <v>33</v>
+      </c>
+      <c r="J32"/>
+      <c r="K32" t="s">
+        <v>265</v>
+      </c>
+      <c r="L32"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>305</v>
+      </c>
+      <c r="B33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" t="s">
+        <v>306</v>
+      </c>
+      <c r="D33" t="s">
+        <v>307</v>
+      </c>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33" t="s">
+        <v>265</v>
+      </c>
+      <c r="L33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>305</v>
+      </c>
+      <c r="B34" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" t="s">
+        <v>308</v>
+      </c>
+      <c r="D34" t="s">
+        <v>309</v>
+      </c>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34" t="s">
+        <v>265</v>
+      </c>
+      <c r="L34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>254</v>
+      </c>
+      <c r="B35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" t="s">
+        <v>310</v>
+      </c>
+      <c r="D35" t="s">
+        <v>311</v>
+      </c>
+      <c r="E35" t="s">
+        <v>209</v>
+      </c>
+      <c r="F35"/>
+      <c r="G35" t="n">
+        <v>50</v>
+      </c>
+      <c r="H35" t="s">
+        <v>257</v>
+      </c>
+      <c r="I35" t="s">
+        <v>258</v>
+      </c>
+      <c r="J35"/>
+      <c r="K35" t="s">
+        <v>265</v>
+      </c>
+      <c r="L35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>254</v>
+      </c>
+      <c r="B36" t="s">
+        <v>201</v>
+      </c>
+      <c r="C36" t="s">
+        <v>310</v>
+      </c>
+      <c r="D36" t="s">
+        <v>311</v>
+      </c>
+      <c r="E36" t="s">
+        <v>233</v>
+      </c>
+      <c r="F36"/>
+      <c r="G36" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" t="s">
+        <v>257</v>
+      </c>
+      <c r="I36" t="s">
+        <v>258</v>
+      </c>
+      <c r="J36"/>
+      <c r="K36" t="s">
+        <v>265</v>
+      </c>
+      <c r="L36"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>254</v>
+      </c>
+      <c r="B37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C37" t="s">
+        <v>310</v>
+      </c>
+      <c r="D37" t="s">
+        <v>311</v>
+      </c>
+      <c r="E37" t="s">
+        <v>221</v>
+      </c>
+      <c r="F37"/>
+      <c r="G37" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" t="s">
+        <v>257</v>
+      </c>
+      <c r="I37" t="s">
+        <v>258</v>
+      </c>
+      <c r="J37"/>
+      <c r="K37" t="s">
+        <v>265</v>
+      </c>
+      <c r="L37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>254</v>
+      </c>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38" t="s">
+        <v>312</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38" t="s">
+        <v>265</v>
+      </c>
+      <c r="L38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>254</v>
+      </c>
+      <c r="B39" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39"/>
+      <c r="D39" t="s">
+        <v>313</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K39" t="s">
+        <v>265</v>
+      </c>
+      <c r="L39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>254</v>
+      </c>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40" t="s">
+        <v>315</v>
+      </c>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40" t="s">
+        <v>265</v>
+      </c>
+      <c r="L40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>254</v>
+      </c>
+      <c r="B41" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" t="s">
+        <v>316</v>
+      </c>
+      <c r="D41" t="s">
+        <v>317</v>
+      </c>
+      <c r="E41" t="s">
+        <v>209</v>
+      </c>
+      <c r="F41"/>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="s">
+        <v>257</v>
+      </c>
+      <c r="I41" t="s">
+        <v>258</v>
+      </c>
+      <c r="J41"/>
+      <c r="K41" t="s">
+        <v>265</v>
+      </c>
+      <c r="L41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>254</v>
+      </c>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42" t="s">
+        <v>318</v>
+      </c>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42" t="s">
+        <v>265</v>
+      </c>
+      <c r="L42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43" t="s">
+        <v>319</v>
+      </c>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43" t="s">
+        <v>265</v>
+      </c>
+      <c r="L43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>274</v>
+      </c>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44" t="s">
+        <v>320</v>
+      </c>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44" t="s">
+        <v>321</v>
+      </c>
+      <c r="K44" t="s">
+        <v>265</v>
+      </c>
+      <c r="L44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>305</v>
+      </c>
+      <c r="B45" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" t="s">
+        <v>322</v>
+      </c>
+      <c r="D45" t="s">
+        <v>323</v>
+      </c>
+      <c r="E45" t="s">
+        <v>209</v>
+      </c>
+      <c r="F45"/>
+      <c r="G45" t="n">
+        <v>10</v>
+      </c>
+      <c r="H45" t="s">
+        <v>192</v>
+      </c>
+      <c r="I45" t="s">
+        <v>324</v>
+      </c>
+      <c r="J45"/>
+      <c r="K45" t="s">
+        <v>279</v>
+      </c>
+      <c r="L45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>305</v>
+      </c>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46" t="s">
+        <v>325</v>
+      </c>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46" t="s">
+        <v>265</v>
+      </c>
+      <c r="L46"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>326</v>
+      </c>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47" t="s">
+        <v>327</v>
+      </c>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47" t="s">
+        <v>265</v>
+      </c>
+      <c r="L47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>254</v>
+      </c>
+      <c r="B48" t="s">
+        <v>201</v>
+      </c>
+      <c r="C48" t="s">
+        <v>328</v>
+      </c>
+      <c r="D48" t="s">
+        <v>329</v>
+      </c>
+      <c r="E48" t="s">
+        <v>221</v>
+      </c>
+      <c r="F48"/>
+      <c r="G48" t="n">
+        <v>100</v>
+      </c>
+      <c r="H48" t="s">
+        <v>257</v>
+      </c>
+      <c r="I48" t="s">
+        <v>258</v>
+      </c>
+      <c r="J48"/>
+      <c r="K48" t="s">
+        <v>265</v>
+      </c>
+      <c r="L48"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49" t="s">
+        <v>330</v>
+      </c>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49" t="s">
+        <v>265</v>
+      </c>
+      <c r="L49"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>254</v>
+      </c>
+      <c r="B50" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" t="s">
+        <v>331</v>
+      </c>
+      <c r="D50" t="s">
+        <v>332</v>
+      </c>
+      <c r="E50" t="s">
+        <v>221</v>
+      </c>
+      <c r="F50"/>
+      <c r="G50" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H50" t="s">
+        <v>257</v>
+      </c>
+      <c r="I50" t="s">
+        <v>258</v>
+      </c>
+      <c r="J50"/>
+      <c r="K50" t="s">
+        <v>265</v>
+      </c>
+      <c r="L50"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>326</v>
+      </c>
+      <c r="B51" t="s">
+        <v>201</v>
+      </c>
+      <c r="C51" t="s">
+        <v>333</v>
+      </c>
+      <c r="D51" t="s">
+        <v>333</v>
+      </c>
+      <c r="E51" t="s">
+        <v>203</v>
+      </c>
+      <c r="F51"/>
+      <c r="G51" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H51" t="s">
+        <v>334</v>
+      </c>
+      <c r="I51" t="s">
+        <v>335</v>
+      </c>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>326</v>
+      </c>
+      <c r="B52" t="s">
+        <v>201</v>
+      </c>
+      <c r="C52" t="s">
+        <v>333</v>
+      </c>
+      <c r="D52" t="s">
+        <v>333</v>
+      </c>
+      <c r="E52" t="s">
+        <v>199</v>
+      </c>
+      <c r="F52"/>
+      <c r="G52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H52" t="s">
+        <v>334</v>
+      </c>
+      <c r="I52" t="s">
+        <v>335</v>
+      </c>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" t="s">
+        <v>190</v>
+      </c>
+      <c r="E53" t="s">
+        <v>191</v>
+      </c>
+      <c r="F53"/>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>192</v>
+      </c>
+      <c r="I53" t="s">
+        <v>193</v>
+      </c>
+      <c r="J53" t="s">
+        <v>194</v>
+      </c>
+      <c r="K53"/>
+      <c r="L53"/>
+    </row>
+    <row r="54">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54" t="s">
+        <v>33</v>
+      </c>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>336</v>
+      </c>
+      <c r="B55" t="s">
+        <v>201</v>
+      </c>
+      <c r="C55"/>
+      <c r="D55" t="s">
+        <v>337</v>
+      </c>
+      <c r="E55" t="s">
+        <v>235</v>
+      </c>
+      <c r="F55"/>
+      <c r="G55" t="n">
+        <v>20</v>
+      </c>
+      <c r="H55" t="s">
+        <v>338</v>
+      </c>
+      <c r="I55" t="s">
+        <v>339</v>
+      </c>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>336</v>
+      </c>
+      <c r="B56" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56"/>
+      <c r="D56" t="s">
+        <v>337</v>
+      </c>
+      <c r="E56" t="s">
+        <v>239</v>
+      </c>
+      <c r="F56"/>
+      <c r="G56" t="n">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>338</v>
+      </c>
+      <c r="I56" t="s">
+        <v>339</v>
+      </c>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>336</v>
+      </c>
+      <c r="B57" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57"/>
+      <c r="D57" t="s">
+        <v>337</v>
+      </c>
+      <c r="E57" t="s">
+        <v>237</v>
+      </c>
+      <c r="F57"/>
+      <c r="G57" t="n">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
+        <v>338</v>
+      </c>
+      <c r="I57" t="s">
+        <v>339</v>
+      </c>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>336</v>
+      </c>
+      <c r="B58" t="s">
+        <v>201</v>
+      </c>
+      <c r="C58"/>
+      <c r="D58" t="s">
+        <v>295</v>
+      </c>
+      <c r="E58" t="s">
+        <v>229</v>
+      </c>
+      <c r="F58"/>
+      <c r="G58" t="n">
+        <v>400</v>
+      </c>
+      <c r="H58" t="s">
+        <v>292</v>
+      </c>
+      <c r="I58" t="s">
+        <v>339</v>
+      </c>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>336</v>
+      </c>
+      <c r="B59" t="s">
+        <v>201</v>
+      </c>
+      <c r="C59"/>
+      <c r="D59" t="s">
+        <v>295</v>
+      </c>
+      <c r="E59" t="s">
+        <v>212</v>
+      </c>
+      <c r="F59"/>
+      <c r="G59" t="n">
+        <v>40</v>
+      </c>
+      <c r="H59" t="s">
+        <v>292</v>
+      </c>
+      <c r="I59" t="s">
+        <v>339</v>
+      </c>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>